--- a/research/traditional_assets/database/data/chile/chile_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0794</v>
+        <v>0.1155</v>
       </c>
       <c r="E2">
-        <v>0.07805000000000001</v>
+        <v>0.1645</v>
       </c>
       <c r="F2">
-        <v>0.2</v>
+        <v>0.109</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>3045</v>
+        <v>4306.8</v>
       </c>
       <c r="L2">
-        <v>0.3294670100192594</v>
+        <v>0.4258845400787137</v>
       </c>
       <c r="M2">
-        <v>1168.173</v>
+        <v>1538.3348</v>
       </c>
       <c r="N2">
-        <v>0.04346835801012872</v>
+        <v>0.05089442202077682</v>
       </c>
       <c r="O2">
-        <v>0.3836364532019704</v>
+        <v>0.35718742453794</v>
       </c>
       <c r="P2">
-        <v>1167.4</v>
+        <v>1533.0048</v>
       </c>
       <c r="Q2">
-        <v>0.04343959425617975</v>
+        <v>0.05071808376894064</v>
       </c>
       <c r="R2">
-        <v>0.3833825944170772</v>
+        <v>0.3559498467539705</v>
       </c>
       <c r="S2">
-        <v>0.7730000000000032</v>
+        <v>5.330000000000005</v>
       </c>
       <c r="T2">
-        <v>0.0006617170573194238</v>
+        <v>0.003464785429023646</v>
       </c>
       <c r="U2">
-        <v>17571.6</v>
+        <v>17256.1</v>
       </c>
       <c r="V2">
-        <v>0.6538488730785403</v>
+        <v>0.5709025342420432</v>
       </c>
       <c r="W2">
-        <v>0.135846458359984</v>
+        <v>0.1537482674803229</v>
       </c>
       <c r="X2">
-        <v>0.1536165993586699</v>
+        <v>0.2173052025885941</v>
       </c>
       <c r="Y2">
-        <v>-0.01777014099868587</v>
+        <v>-0.06355693510827115</v>
       </c>
       <c r="Z2">
-        <v>0.0684615014240899</v>
+        <v>0.0754134742877086</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04421068298844757</v>
+        <v>0.07156159315416324</v>
       </c>
       <c r="AC2">
-        <v>-0.04421068298844757</v>
+        <v>-0.07156159315416324</v>
       </c>
       <c r="AD2">
-        <v>131049.6</v>
+        <v>144116.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>131049.6</v>
+        <v>144116.5</v>
       </c>
       <c r="AG2">
-        <v>113478</v>
+        <v>126860.4</v>
       </c>
       <c r="AH2">
-        <v>0.8298285817771494</v>
+        <v>0.8266286189540702</v>
       </c>
       <c r="AI2">
-        <v>0.8563581437261527</v>
+        <v>0.8695624628547466</v>
       </c>
       <c r="AJ2">
-        <v>0.8085237057372138</v>
+        <v>0.8075835973069597</v>
       </c>
       <c r="AK2">
-        <v>0.8377251684449323</v>
+        <v>0.854403064688197</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Grupo Security S.A. (SNSE:SECURITY)</t>
+          <t>Scotiabank Chile S.A. (SNSE:SCOTIABKCL)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0286</v>
+        <v>0.223</v>
       </c>
       <c r="E3">
-        <v>0.0302</v>
+        <v>0.383</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,85 +731,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>104.8</v>
+        <v>505.5</v>
       </c>
       <c r="L3">
-        <v>0.2324240408072744</v>
+        <v>0.4152974038777522</v>
       </c>
       <c r="M3">
-        <v>43.373</v>
+        <v>176.8</v>
       </c>
       <c r="N3">
-        <v>0.07665782962177449</v>
+        <v>0.03988089867364433</v>
       </c>
       <c r="O3">
-        <v>0.413864503816794</v>
+        <v>0.3497527200791296</v>
       </c>
       <c r="P3">
-        <v>42.6</v>
+        <v>176.8</v>
       </c>
       <c r="Q3">
-        <v>0.07529162248144221</v>
+        <v>0.03988089867364433</v>
       </c>
       <c r="R3">
-        <v>0.4064885496183206</v>
+        <v>0.3497527200791296</v>
       </c>
       <c r="S3">
-        <v>0.7730000000000032</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.01782214741890123</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>932.8</v>
+        <v>1160.1</v>
       </c>
       <c r="V3">
-        <v>1.648639095086603</v>
+        <v>0.2616845619417125</v>
       </c>
       <c r="W3">
-        <v>0.09894259818731117</v>
+        <v>0.1574570147022178</v>
       </c>
       <c r="X3">
-        <v>0.298734965040353</v>
+        <v>0.2071877518384542</v>
       </c>
       <c r="Y3">
-        <v>-0.1997923668530418</v>
+        <v>-0.04973073713623638</v>
       </c>
       <c r="Z3">
-        <v>0.06874523555420034</v>
+        <v>0.04779893972118594</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04175894702939699</v>
+        <v>0.07031957320205898</v>
       </c>
       <c r="AC3">
-        <v>-0.04175894702939699</v>
+        <v>-0.07031957320205898</v>
       </c>
       <c r="AD3">
-        <v>7146.4</v>
+        <v>25207.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>7146.4</v>
+        <v>25207.2</v>
       </c>
       <c r="AG3">
-        <v>6213.599999999999</v>
+        <v>24047.1</v>
       </c>
       <c r="AH3">
-        <v>0.9266357200280075</v>
+        <v>0.8504338672892403</v>
       </c>
       <c r="AI3">
-        <v>0.8695715658956232</v>
+        <v>0.8887823281561271</v>
       </c>
       <c r="AJ3">
-        <v>0.9165412868395433</v>
+        <v>0.8443415273013276</v>
       </c>
       <c r="AK3">
-        <v>0.8528721432983323</v>
+        <v>0.8840390568132523</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0344</v>
+        <v>0.124</v>
       </c>
       <c r="E4">
-        <v>0.0226</v>
+        <v>0.194</v>
       </c>
       <c r="F4">
-        <v>0.2</v>
+        <v>0.109</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,28 +856,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>784.8</v>
+        <v>1406.7</v>
       </c>
       <c r="L4">
-        <v>0.3745704467353952</v>
+        <v>0.5245553193869561</v>
       </c>
       <c r="M4">
-        <v>272.1</v>
+        <v>562.3</v>
       </c>
       <c r="N4">
-        <v>0.03455940254527905</v>
+        <v>0.05374227030746733</v>
       </c>
       <c r="O4">
-        <v>0.3467125382262997</v>
+        <v>0.3997298642212269</v>
       </c>
       <c r="P4">
-        <v>272.1</v>
+        <v>562.3</v>
       </c>
       <c r="Q4">
-        <v>0.03455940254527905</v>
+        <v>0.05374227030746733</v>
       </c>
       <c r="R4">
-        <v>0.3467125382262997</v>
+        <v>0.3997298642212269</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -886,55 +886,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>2498.2</v>
+        <v>3073.4</v>
       </c>
       <c r="V4">
-        <v>0.3172962125638225</v>
+        <v>0.2937426526106529</v>
       </c>
       <c r="W4">
-        <v>0.1700357491062723</v>
+        <v>0.2818021555350775</v>
       </c>
       <c r="X4">
-        <v>0.09505918165971237</v>
+        <v>0.1189856709752889</v>
       </c>
       <c r="Y4">
-        <v>0.07497656744655996</v>
+        <v>0.1628164845597887</v>
       </c>
       <c r="Z4">
-        <v>0.09074490339513792</v>
+        <v>0.1177046345349445</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04365015333543473</v>
+        <v>0.07057436654895874</v>
       </c>
       <c r="AC4">
-        <v>-0.04365015333543473</v>
+        <v>-0.07057436654895874</v>
       </c>
       <c r="AD4">
-        <v>20289.7</v>
+        <v>20822.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>20289.7</v>
+        <v>20822.4</v>
       </c>
       <c r="AG4">
-        <v>17791.5</v>
+        <v>17749</v>
       </c>
       <c r="AH4">
-        <v>0.7204356054553654</v>
+        <v>0.6655649778010759</v>
       </c>
       <c r="AI4">
-        <v>0.8025512726697388</v>
+        <v>0.8101218544283113</v>
       </c>
       <c r="AJ4">
-        <v>0.6932230400274304</v>
+        <v>0.6291316784761041</v>
       </c>
       <c r="AK4">
-        <v>0.7809009230445106</v>
+        <v>0.7843336544495214</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -951,7 +951,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Scotiabank Chile S.A. (SNSE:SCOTIABKCL)</t>
+          <t>Banco Santander-Chile (SNSE:BSANTANDER)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -960,10 +960,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.207</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="E5">
-        <v>0.291</v>
+        <v>0.131</v>
+      </c>
+      <c r="F5">
+        <v>0.0287</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -978,28 +981,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>460.4</v>
+        <v>1044.4</v>
       </c>
       <c r="L5">
-        <v>0.3386788288951008</v>
+        <v>0.4667500893814802</v>
       </c>
       <c r="M5">
-        <v>136.1</v>
+        <v>484.3</v>
       </c>
       <c r="N5">
-        <v>0.02814134772450013</v>
+        <v>0.06431521493738462</v>
       </c>
       <c r="O5">
-        <v>0.2956125108601216</v>
+        <v>0.4637112217541172</v>
       </c>
       <c r="P5">
-        <v>136.1</v>
+        <v>484.3</v>
       </c>
       <c r="Q5">
-        <v>0.02814134772450013</v>
+        <v>0.06431521493738462</v>
       </c>
       <c r="R5">
-        <v>0.2956125108601216</v>
+        <v>0.4637112217541172</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1008,55 +1011,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>1460.7</v>
+        <v>3209</v>
       </c>
       <c r="V5">
-        <v>0.3020284101482538</v>
+        <v>0.4261563591452969</v>
       </c>
       <c r="W5">
-        <v>0.1529466480632516</v>
+        <v>0.2574887206922907</v>
       </c>
       <c r="X5">
-        <v>0.1421938774900638</v>
+        <v>0.199686435546647</v>
       </c>
       <c r="Y5">
-        <v>0.01075277057318785</v>
+        <v>0.05780228514564364</v>
       </c>
       <c r="Z5">
-        <v>0.0582119335748482</v>
+        <v>0.06470623957155539</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.04377221638588336</v>
+        <v>0.07156060338398457</v>
       </c>
       <c r="AC5">
-        <v>-0.04377221638588336</v>
+        <v>-0.07156060338398457</v>
       </c>
       <c r="AD5">
-        <v>23715.3</v>
+        <v>40449.3</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>23715.3</v>
+        <v>40449.3</v>
       </c>
       <c r="AG5">
-        <v>22254.6</v>
+        <v>37240.3</v>
       </c>
       <c r="AH5">
-        <v>0.8306119446896146</v>
+        <v>0.8430555613450773</v>
       </c>
       <c r="AI5">
-        <v>0.875610593591121</v>
+        <v>0.9072767320425631</v>
       </c>
       <c r="AJ5">
-        <v>0.8214787991539595</v>
+        <v>0.8318062827225131</v>
       </c>
       <c r="AK5">
-        <v>0.8685196459513885</v>
+        <v>0.9000850771736976</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1073,7 +1076,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Banco Santander-Chile (SNSE:BSANTANDER)</t>
+          <t>Banco de Crédito e Inversiones (SNSE:BCI)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1082,13 +1085,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.07150000000000001</v>
+        <v>0.127</v>
       </c>
       <c r="E6">
-        <v>0.109</v>
+        <v>0.135</v>
       </c>
       <c r="F6">
-        <v>0.129</v>
+        <v>0.149</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1103,28 +1106,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>926.4</v>
+        <v>787.3</v>
       </c>
       <c r="L6">
-        <v>0.4099477829896451</v>
+        <v>0.3625938377930272</v>
       </c>
       <c r="M6">
-        <v>588</v>
+        <v>163.9048</v>
       </c>
       <c r="N6">
-        <v>0.07779835935432654</v>
+        <v>0.03381711644796567</v>
       </c>
       <c r="O6">
-        <v>0.6347150259067358</v>
+        <v>0.2081859519878064</v>
       </c>
       <c r="P6">
-        <v>588</v>
+        <v>163.9048</v>
       </c>
       <c r="Q6">
-        <v>0.07779835935432654</v>
+        <v>0.03381711644796567</v>
       </c>
       <c r="R6">
-        <v>0.6347150259067358</v>
+        <v>0.2081859519878064</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1133,55 +1136,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>3926.1</v>
+        <v>4654.7</v>
       </c>
       <c r="V6">
-        <v>0.5194628208520773</v>
+        <v>0.9603656020467112</v>
       </c>
       <c r="W6">
-        <v>0.1998662380531164</v>
+        <v>0.1464853198377553</v>
       </c>
       <c r="X6">
-        <v>0.1351964193647191</v>
+        <v>0.227422653338734</v>
       </c>
       <c r="Y6">
-        <v>0.0646698186883973</v>
+        <v>-0.0809373335009787</v>
       </c>
       <c r="Z6">
-        <v>0.06736943780296571</v>
+        <v>0.07541854810698161</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.04464914959101179</v>
+        <v>0.07156258292434192</v>
       </c>
       <c r="AC6">
-        <v>-0.04464914959101179</v>
+        <v>-0.07156258292434192</v>
       </c>
       <c r="AD6">
-        <v>34450.9</v>
+        <v>31668.5</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>34450.9</v>
+        <v>31668.5</v>
       </c>
       <c r="AG6">
-        <v>30524.8</v>
+        <v>27013.8</v>
       </c>
       <c r="AH6">
-        <v>0.8200857437352561</v>
+        <v>0.8672665978370709</v>
       </c>
       <c r="AI6">
-        <v>0.8920504713891025</v>
+        <v>0.8621243510621212</v>
       </c>
       <c r="AJ6">
-        <v>0.8015377020597225</v>
+        <v>0.8478748046176156</v>
       </c>
       <c r="AK6">
-        <v>0.8798344372769774</v>
+        <v>0.8421180607511596</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1198,7 +1201,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Banco de Crédito e Inversiones (SNSE:BCI)</t>
+          <t>Itaú Corpbanca (SNSE:ITAUCORP)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1207,13 +1210,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0873</v>
+        <v>0.107</v>
       </c>
       <c r="E7">
-        <v>0.0723</v>
-      </c>
-      <c r="F7">
-        <v>0.258</v>
+        <v>0.5589999999999999</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1228,28 +1228,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>596.7</v>
+        <v>436.6</v>
       </c>
       <c r="L7">
-        <v>0.2946230188120279</v>
+        <v>0.331989962740476</v>
       </c>
       <c r="M7">
-        <v>128.6</v>
+        <v>86.8</v>
       </c>
       <c r="N7">
-        <v>0.02830417079344118</v>
+        <v>0.04050963737340738</v>
       </c>
       <c r="O7">
-        <v>0.2155186861069214</v>
+        <v>0.1988089784699954</v>
       </c>
       <c r="P7">
-        <v>128.6</v>
+        <v>86.8</v>
       </c>
       <c r="Q7">
-        <v>0.02830417079344118</v>
+        <v>0.04050963737340738</v>
       </c>
       <c r="R7">
-        <v>0.2155186861069214</v>
+        <v>0.1988089784699954</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1258,55 +1258,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>3778.9</v>
+        <v>4348.5</v>
       </c>
       <c r="V7">
-        <v>0.8317156377242214</v>
+        <v>2.029448826247258</v>
       </c>
       <c r="W7">
-        <v>0.1187462686567164</v>
+        <v>0.1500395202584281</v>
       </c>
       <c r="X7">
-        <v>0.165039321227276</v>
+        <v>0.2846676733767605</v>
       </c>
       <c r="Y7">
-        <v>-0.04629305257055959</v>
+        <v>-0.1346281531183324</v>
       </c>
       <c r="Z7">
-        <v>0.06915496612762237</v>
+        <v>0.08555777475619512</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.04473175007014355</v>
+        <v>0.0728125627314099</v>
       </c>
       <c r="AC7">
-        <v>-0.04473175007014355</v>
+        <v>-0.0728125627314099</v>
       </c>
       <c r="AD7">
-        <v>27403.1</v>
+        <v>19139.9</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>27403.1</v>
+        <v>19139.9</v>
       </c>
       <c r="AG7">
-        <v>23624.2</v>
+        <v>14791.4</v>
       </c>
       <c r="AH7">
-        <v>0.8577782925256522</v>
+        <v>0.8993215114694633</v>
       </c>
       <c r="AI7">
-        <v>0.8359854054680683</v>
+        <v>0.8472243739846754</v>
       </c>
       <c r="AJ7">
-        <v>0.8386982252722089</v>
+        <v>0.8734683272214053</v>
       </c>
       <c r="AK7">
-        <v>0.8146135411458423</v>
+        <v>0.8108075514723616</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Itaú Corpbanca (SNSE:ITAUCORP)</t>
+          <t>Grupo Security S.A. (SNSE:SECURITY)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.09429999999999999</v>
+        <v>0.0693</v>
       </c>
       <c r="E8">
-        <v>0.08380000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1350,82 +1350,85 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>171.9</v>
+        <v>126.3</v>
       </c>
       <c r="L8">
-        <v>0.1634651958919741</v>
+        <v>0.2579130079640596</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>64.23</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>0.07926693817104777</v>
       </c>
       <c r="O8">
-        <v>-0</v>
+        <v>0.5085510688836105</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>58.9</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.07268912748364803</v>
       </c>
       <c r="R8">
-        <v>-0</v>
+        <v>0.4663499604117181</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>5.330000000000005</v>
+      </c>
+      <c r="T8">
+        <v>0.08298302973688315</v>
       </c>
       <c r="U8">
-        <v>4974.9</v>
+        <v>810.4</v>
       </c>
       <c r="V8">
-        <v>3.323024514060517</v>
+        <v>1.000123411082315</v>
       </c>
       <c r="W8">
-        <v>0.05418439716312057</v>
+        <v>0.1215825953022718</v>
       </c>
       <c r="X8">
-        <v>0.2870284737679635</v>
+        <v>0.272624986234163</v>
       </c>
       <c r="Y8">
-        <v>-0.232844076604843</v>
+        <v>-0.1510423909318911</v>
       </c>
       <c r="Z8">
-        <v>0.05486169802068008</v>
+        <v>0.06892038337578991</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.04692924246707656</v>
+        <v>0.07404453293086705</v>
       </c>
       <c r="AC8">
-        <v>-0.04692924246707656</v>
+        <v>-0.07404453293086705</v>
       </c>
       <c r="AD8">
-        <v>18044.2</v>
+        <v>6829.2</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>18044.2</v>
+        <v>6829.2</v>
       </c>
       <c r="AG8">
-        <v>13069.3</v>
+        <v>6018.8</v>
       </c>
       <c r="AH8">
-        <v>0.9233879015213933</v>
+        <v>0.8939328490084429</v>
       </c>
       <c r="AI8">
-        <v>0.8572921764166496</v>
+        <v>0.8797567825213202</v>
       </c>
       <c r="AJ8">
-        <v>0.8972223747803163</v>
+        <v>0.8813460045979704</v>
       </c>
       <c r="AK8">
-        <v>0.8131213836869284</v>
+        <v>0.8657403411869624</v>
       </c>
       <c r="AL8">
         <v>0</v>

--- a/research/traditional_assets/database/data/chile/chile_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ8"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.1155</v>
+        <v>0.04480000000000001</v>
       </c>
       <c r="E2">
-        <v>0.1645</v>
+        <v>0.159</v>
       </c>
       <c r="F2">
-        <v>0.109</v>
+        <v>-0.0203</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>4306.8</v>
+        <v>3194.6</v>
       </c>
       <c r="L2">
-        <v>0.4258845400787137</v>
+        <v>0.3868350629064093</v>
       </c>
       <c r="M2">
-        <v>1538.3348</v>
+        <v>2019.4</v>
       </c>
       <c r="N2">
-        <v>0.05089442202077682</v>
+        <v>0.06809552391807226</v>
       </c>
       <c r="O2">
-        <v>0.35718742453794</v>
+        <v>0.6321292180554686</v>
       </c>
       <c r="P2">
-        <v>1533.0048</v>
+        <v>2019.4</v>
       </c>
       <c r="Q2">
-        <v>0.05071808376894064</v>
+        <v>0.06809552391807226</v>
       </c>
       <c r="R2">
-        <v>0.3559498467539705</v>
+        <v>0.6321292180554686</v>
       </c>
       <c r="S2">
-        <v>5.330000000000005</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.003464785429023646</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>17256.1</v>
+        <v>18337.9</v>
       </c>
       <c r="V2">
-        <v>0.5709025342420432</v>
+        <v>0.6183663009097837</v>
       </c>
       <c r="W2">
-        <v>0.1537482674803229</v>
+        <v>0.1531442565966187</v>
       </c>
       <c r="X2">
-        <v>0.2173052025885941</v>
+        <v>0.1326817962982215</v>
       </c>
       <c r="Y2">
-        <v>-0.06355693510827115</v>
+        <v>0.02046246029839724</v>
       </c>
       <c r="Z2">
-        <v>0.0754134742877086</v>
+        <v>0.06853935475089612</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07156159315416324</v>
+        <v>0.06084900905472118</v>
       </c>
       <c r="AC2">
-        <v>-0.07156159315416324</v>
+        <v>-0.06084900905472118</v>
       </c>
       <c r="AD2">
-        <v>144116.5</v>
+        <v>111963.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>144116.5</v>
+        <v>111963.2</v>
       </c>
       <c r="AG2">
-        <v>126860.4</v>
+        <v>93625.29999999999</v>
       </c>
       <c r="AH2">
-        <v>0.8266286189540702</v>
+        <v>0.7905967154032026</v>
       </c>
       <c r="AI2">
-        <v>0.8695624628547466</v>
+        <v>0.8383999568681161</v>
       </c>
       <c r="AJ2">
-        <v>0.8075835973069597</v>
+        <v>0.7594481536850456</v>
       </c>
       <c r="AK2">
-        <v>0.854403064688197</v>
+        <v>0.8126772911133101</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Scotiabank Chile S.A. (SNSE:SCOTIABKCL)</t>
+          <t>Banco de Chile (SNSE:CHILE)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,10 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.223</v>
+        <v>0.112</v>
       </c>
       <c r="E3">
-        <v>0.383</v>
+        <v>0.159</v>
+      </c>
+      <c r="F3">
+        <v>-0.0629</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,28 +734,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>505.5</v>
+        <v>1349</v>
       </c>
       <c r="L3">
-        <v>0.4152974038777522</v>
+        <v>0.4665237238898879</v>
       </c>
       <c r="M3">
-        <v>176.8</v>
+        <v>970.7</v>
       </c>
       <c r="N3">
-        <v>0.03988089867364433</v>
+        <v>0.08137789961687752</v>
       </c>
       <c r="O3">
-        <v>0.3497527200791296</v>
+        <v>0.7195700518902891</v>
       </c>
       <c r="P3">
-        <v>176.8</v>
+        <v>970.7</v>
       </c>
       <c r="Q3">
-        <v>0.03988089867364433</v>
+        <v>0.08137789961687752</v>
       </c>
       <c r="R3">
-        <v>0.3497527200791296</v>
+        <v>0.7195700518902891</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -761,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1160.1</v>
+        <v>3233.2</v>
       </c>
       <c r="V3">
-        <v>0.2616845619417125</v>
+        <v>0.271052874257019</v>
       </c>
       <c r="W3">
-        <v>0.1574570147022178</v>
+        <v>0.276411769527088</v>
       </c>
       <c r="X3">
-        <v>0.2071877518384542</v>
+        <v>0.09195440810251884</v>
       </c>
       <c r="Y3">
-        <v>-0.04973073713623638</v>
+        <v>0.1844573614245691</v>
       </c>
       <c r="Z3">
-        <v>0.04779893972118594</v>
+        <v>0.1277806746975174</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07031957320205898</v>
+        <v>0.06041354841159265</v>
       </c>
       <c r="AC3">
-        <v>-0.07031957320205898</v>
+        <v>-0.06041354841159265</v>
       </c>
       <c r="AD3">
-        <v>25207.2</v>
+        <v>21457.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>25207.2</v>
+        <v>21457.2</v>
       </c>
       <c r="AG3">
-        <v>24047.1</v>
+        <v>18224</v>
       </c>
       <c r="AH3">
-        <v>0.8504338672892403</v>
+        <v>0.6427101586017883</v>
       </c>
       <c r="AI3">
-        <v>0.8887823281561271</v>
+        <v>0.792211244517301</v>
       </c>
       <c r="AJ3">
-        <v>0.8443415273013276</v>
+        <v>0.6043983377719113</v>
       </c>
       <c r="AK3">
-        <v>0.8840390568132523</v>
+        <v>0.7640449438202247</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -826,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Banco de Chile (SNSE:CHILE)</t>
+          <t>Banco de Crédito e Inversiones (SNSE:BCI)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -835,13 +838,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.124</v>
+        <v>0.103</v>
       </c>
       <c r="E4">
-        <v>0.194</v>
+        <v>0.14</v>
       </c>
       <c r="F4">
-        <v>0.109</v>
+        <v>-0.0203</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,28 +859,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>1406.7</v>
+        <v>775.4</v>
       </c>
       <c r="L4">
-        <v>0.5245553193869561</v>
+        <v>0.334685773480663</v>
       </c>
       <c r="M4">
-        <v>562.3</v>
+        <v>283.6</v>
       </c>
       <c r="N4">
-        <v>0.05374227030746733</v>
+        <v>0.05466777184494093</v>
       </c>
       <c r="O4">
-        <v>0.3997298642212269</v>
+        <v>0.3657467113747743</v>
       </c>
       <c r="P4">
-        <v>562.3</v>
+        <v>283.6</v>
       </c>
       <c r="Q4">
-        <v>0.05374227030746733</v>
+        <v>0.05466777184494093</v>
       </c>
       <c r="R4">
-        <v>0.3997298642212269</v>
+        <v>0.3657467113747743</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -886,55 +889,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>3073.4</v>
+        <v>3836.3</v>
       </c>
       <c r="V4">
-        <v>0.2937426526106529</v>
+        <v>0.7394992000308422</v>
       </c>
       <c r="W4">
-        <v>0.2818021555350775</v>
+        <v>0.1531442565966187</v>
       </c>
       <c r="X4">
-        <v>0.1189856709752889</v>
+        <v>0.1638608914784369</v>
       </c>
       <c r="Y4">
-        <v>0.1628164845597887</v>
+        <v>-0.01071663488181812</v>
       </c>
       <c r="Z4">
-        <v>0.1177046345349445</v>
+        <v>0.07223701523437744</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.07057436654895874</v>
+        <v>0.06079128207260086</v>
       </c>
       <c r="AC4">
-        <v>-0.07057436654895874</v>
+        <v>-0.06079128207260086</v>
       </c>
       <c r="AD4">
-        <v>20822.4</v>
+        <v>31569.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>20822.4</v>
+        <v>31569.4</v>
       </c>
       <c r="AG4">
-        <v>17749</v>
+        <v>27733.1</v>
       </c>
       <c r="AH4">
-        <v>0.6655649778010759</v>
+        <v>0.8588653620661043</v>
       </c>
       <c r="AI4">
-        <v>0.8101218544283113</v>
+        <v>0.8418798518348636</v>
       </c>
       <c r="AJ4">
-        <v>0.6291316784761041</v>
+        <v>0.842418774756385</v>
       </c>
       <c r="AK4">
-        <v>0.7843336544495214</v>
+        <v>0.8238598555064405</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -960,13 +963,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.08119999999999999</v>
+        <v>-0.0109</v>
       </c>
       <c r="E5">
-        <v>0.131</v>
+        <v>-0.0654</v>
       </c>
       <c r="F5">
-        <v>0.0287</v>
+        <v>0.04849999999999999</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -981,28 +984,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>1044.4</v>
+        <v>453.4</v>
       </c>
       <c r="L5">
-        <v>0.4667500893814802</v>
+        <v>0.2992936827513367</v>
       </c>
       <c r="M5">
-        <v>484.3</v>
+        <v>543.3</v>
       </c>
       <c r="N5">
-        <v>0.06431521493738462</v>
+        <v>0.05876245173431973</v>
       </c>
       <c r="O5">
-        <v>0.4637112217541172</v>
+        <v>1.198279664755183</v>
       </c>
       <c r="P5">
-        <v>484.3</v>
+        <v>543.3</v>
       </c>
       <c r="Q5">
-        <v>0.06431521493738462</v>
+        <v>0.05876245173431973</v>
       </c>
       <c r="R5">
-        <v>0.4637112217541172</v>
+        <v>1.198279664755183</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1011,55 +1014,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>3209</v>
+        <v>4972.6</v>
       </c>
       <c r="V5">
-        <v>0.4261563591452969</v>
+        <v>0.5378283959029603</v>
       </c>
       <c r="W5">
-        <v>0.2574887206922907</v>
+        <v>0.1127047652191205</v>
       </c>
       <c r="X5">
-        <v>0.199686435546647</v>
+        <v>0.1326817962982215</v>
       </c>
       <c r="Y5">
-        <v>0.05780228514564364</v>
+        <v>-0.01997703107910097</v>
       </c>
       <c r="Z5">
-        <v>0.06470623957155539</v>
+        <v>0.03671310029275481</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.07156060338398457</v>
+        <v>0.06084900905472118</v>
       </c>
       <c r="AC5">
-        <v>-0.07156060338398457</v>
+        <v>-0.06084900905472118</v>
       </c>
       <c r="AD5">
-        <v>40449.3</v>
+        <v>39079.2</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>40449.3</v>
+        <v>39079.2</v>
       </c>
       <c r="AG5">
-        <v>37240.3</v>
+        <v>34106.6</v>
       </c>
       <c r="AH5">
-        <v>0.8430555613450773</v>
+        <v>0.8086762724806467</v>
       </c>
       <c r="AI5">
-        <v>0.9072767320425631</v>
+        <v>0.8899090716564535</v>
       </c>
       <c r="AJ5">
-        <v>0.8318062827225131</v>
+        <v>0.786731038491614</v>
       </c>
       <c r="AK5">
-        <v>0.9000850771736976</v>
+        <v>0.8758509646620152</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1076,7 +1079,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Banco de Crédito e Inversiones (SNSE:BCI)</t>
+          <t>Banco Itaú Chile (SNSE:ITAUCL)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1085,13 +1088,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.127</v>
+        <v>0.04480000000000001</v>
       </c>
       <c r="E6">
-        <v>0.135</v>
-      </c>
-      <c r="F6">
-        <v>0.149</v>
+        <v>0.24</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1106,28 +1106,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>787.3</v>
+        <v>414.5</v>
       </c>
       <c r="L6">
-        <v>0.3625938377930272</v>
+        <v>0.3366907643570791</v>
       </c>
       <c r="M6">
-        <v>163.9048</v>
+        <v>145.7</v>
       </c>
       <c r="N6">
-        <v>0.03381711644796567</v>
+        <v>0.06879456064970017</v>
       </c>
       <c r="O6">
-        <v>0.2081859519878064</v>
+        <v>0.3515078407720145</v>
       </c>
       <c r="P6">
-        <v>163.9048</v>
+        <v>145.7</v>
       </c>
       <c r="Q6">
-        <v>0.03381711644796567</v>
+        <v>0.06879456064970017</v>
       </c>
       <c r="R6">
-        <v>0.2081859519878064</v>
+        <v>0.3515078407720145</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1136,55 +1136,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>4654.7</v>
+        <v>5503.3</v>
       </c>
       <c r="V6">
-        <v>0.9603656020467112</v>
+        <v>2.598470182728174</v>
       </c>
       <c r="W6">
-        <v>0.1464853198377553</v>
+        <v>0.1202076445681805</v>
       </c>
       <c r="X6">
-        <v>0.227422653338734</v>
+        <v>0.2189767928370019</v>
       </c>
       <c r="Y6">
-        <v>-0.0809373335009787</v>
+        <v>-0.09876914826882144</v>
       </c>
       <c r="Z6">
-        <v>0.07541854810698161</v>
+        <v>0.06944930217864677</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.07156258292434192</v>
+        <v>0.06161977638093022</v>
       </c>
       <c r="AC6">
-        <v>-0.07156258292434192</v>
+        <v>-0.06161977638093022</v>
       </c>
       <c r="AD6">
-        <v>31668.5</v>
+        <v>19847</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>31668.5</v>
+        <v>19847</v>
       </c>
       <c r="AG6">
-        <v>27013.8</v>
+        <v>14343.7</v>
       </c>
       <c r="AH6">
-        <v>0.8672665978370709</v>
+        <v>0.9035779812336955</v>
       </c>
       <c r="AI6">
-        <v>0.8621243510621212</v>
+        <v>0.8299843178254052</v>
       </c>
       <c r="AJ6">
-        <v>0.8478748046176156</v>
+        <v>0.8713430043252174</v>
       </c>
       <c r="AK6">
-        <v>0.8421180607511596</v>
+        <v>0.7791593333767899</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Itaú Corpbanca (SNSE:ITAUCORP)</t>
+          <t>Grupo Security S.A. (SNSE:SECURITY)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.107</v>
+        <v>-0.04679999999999999</v>
       </c>
       <c r="E7">
-        <v>0.5589999999999999</v>
+        <v>0.18</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1228,28 +1228,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>436.6</v>
+        <v>202.3</v>
       </c>
       <c r="L7">
-        <v>0.331989962740476</v>
+        <v>0.6656794998354723</v>
       </c>
       <c r="M7">
-        <v>86.8</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="N7">
-        <v>0.04050963737340738</v>
+        <v>0.06472189147814254</v>
       </c>
       <c r="O7">
-        <v>0.1988089784699954</v>
+        <v>0.3761739990113692</v>
       </c>
       <c r="P7">
-        <v>86.8</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="Q7">
-        <v>0.04050963737340738</v>
+        <v>0.06472189147814254</v>
       </c>
       <c r="R7">
-        <v>0.1988089784699954</v>
+        <v>0.3761739990113692</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1258,182 +1258,60 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>4348.5</v>
+        <v>792.5</v>
       </c>
       <c r="V7">
-        <v>2.029448826247258</v>
+        <v>0.6740091852355843</v>
       </c>
       <c r="W7">
-        <v>0.1500395202584281</v>
+        <v>0.2238574748257165</v>
       </c>
       <c r="X7">
-        <v>0.2846676733767605</v>
+        <v>0.06192751386767292</v>
       </c>
       <c r="Y7">
-        <v>-0.1346281531183324</v>
+        <v>0.1619299609580436</v>
       </c>
       <c r="Z7">
-        <v>0.08555777475619512</v>
+        <v>0.04470103699345444</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.0728125627314099</v>
+        <v>0.06173185765722965</v>
       </c>
       <c r="AC7">
-        <v>-0.0728125627314099</v>
+        <v>-0.06173185765722965</v>
       </c>
       <c r="AD7">
-        <v>19139.9</v>
+        <v>10.4</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>19139.9</v>
+        <v>10.4</v>
       </c>
       <c r="AG7">
-        <v>14791.4</v>
+        <v>-782.1</v>
       </c>
       <c r="AH7">
-        <v>0.8993215114694633</v>
+        <v>0.008767492834260664</v>
       </c>
       <c r="AI7">
-        <v>0.8472243739846754</v>
+        <v>0.009172693596754277</v>
       </c>
       <c r="AJ7">
-        <v>0.8734683272214053</v>
+        <v>-1.986537973075946</v>
       </c>
       <c r="AK7">
-        <v>0.8108075514723616</v>
+        <v>-2.291532376208614</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Chile</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Grupo Security S.A. (SNSE:SECURITY)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>0.0693</v>
-      </c>
-      <c r="E8">
-        <v>0.12</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>126.3</v>
-      </c>
-      <c r="L8">
-        <v>0.2579130079640596</v>
-      </c>
-      <c r="M8">
-        <v>64.23</v>
-      </c>
-      <c r="N8">
-        <v>0.07926693817104777</v>
-      </c>
-      <c r="O8">
-        <v>0.5085510688836105</v>
-      </c>
-      <c r="P8">
-        <v>58.9</v>
-      </c>
-      <c r="Q8">
-        <v>0.07268912748364803</v>
-      </c>
-      <c r="R8">
-        <v>0.4663499604117181</v>
-      </c>
-      <c r="S8">
-        <v>5.330000000000005</v>
-      </c>
-      <c r="T8">
-        <v>0.08298302973688315</v>
-      </c>
-      <c r="U8">
-        <v>810.4</v>
-      </c>
-      <c r="V8">
-        <v>1.000123411082315</v>
-      </c>
-      <c r="W8">
-        <v>0.1215825953022718</v>
-      </c>
-      <c r="X8">
-        <v>0.272624986234163</v>
-      </c>
-      <c r="Y8">
-        <v>-0.1510423909318911</v>
-      </c>
-      <c r="Z8">
-        <v>0.06892038337578991</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0.07404453293086705</v>
-      </c>
-      <c r="AC8">
-        <v>-0.07404453293086705</v>
-      </c>
-      <c r="AD8">
-        <v>6829.2</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>6829.2</v>
-      </c>
-      <c r="AG8">
-        <v>6018.8</v>
-      </c>
-      <c r="AH8">
-        <v>0.8939328490084429</v>
-      </c>
-      <c r="AI8">
-        <v>0.8797567825213202</v>
-      </c>
-      <c r="AJ8">
-        <v>0.8813460045979704</v>
-      </c>
-      <c r="AK8">
-        <v>0.8657403411869624</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/chile/chile_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.04480000000000001</v>
+        <v>0.07875</v>
       </c>
       <c r="E2">
-        <v>0.159</v>
+        <v>0.1625</v>
       </c>
       <c r="F2">
-        <v>-0.0203</v>
+        <v>0.116</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,28 +609,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>3194.6</v>
+        <v>4297.9</v>
       </c>
       <c r="L2">
-        <v>0.3868350629064093</v>
+        <v>0.3939955080900215</v>
       </c>
       <c r="M2">
-        <v>2019.4</v>
+        <v>1813.5</v>
       </c>
       <c r="N2">
-        <v>0.06809552391807226</v>
+        <v>0.0565476468882424</v>
       </c>
       <c r="O2">
-        <v>0.6321292180554686</v>
+        <v>0.4219502547755881</v>
       </c>
       <c r="P2">
-        <v>2019.4</v>
+        <v>1813.5</v>
       </c>
       <c r="Q2">
-        <v>0.06809552391807226</v>
+        <v>0.0565476468882424</v>
       </c>
       <c r="R2">
-        <v>0.6321292180554686</v>
+        <v>0.4219502547755881</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>18337.9</v>
+        <v>15572.4</v>
       </c>
       <c r="V2">
-        <v>0.6183663009097837</v>
+        <v>0.4855707617328182</v>
       </c>
       <c r="W2">
-        <v>0.1531442565966187</v>
+        <v>0.1497655924717063</v>
       </c>
       <c r="X2">
-        <v>0.1326817962982215</v>
+        <v>0.1395576007014889</v>
       </c>
       <c r="Y2">
-        <v>0.02046246029839724</v>
+        <v>0.01020799177021736</v>
       </c>
       <c r="Z2">
-        <v>0.06853935475089612</v>
+        <v>0.07511277072030727</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06084900905472118</v>
+        <v>0.06340344550376793</v>
       </c>
       <c r="AC2">
-        <v>-0.06084900905472118</v>
+        <v>-0.06340344550376793</v>
       </c>
       <c r="AD2">
-        <v>111963.2</v>
+        <v>113325.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>111963.2</v>
+        <v>113325.8</v>
       </c>
       <c r="AG2">
-        <v>93625.29999999999</v>
+        <v>97753.40000000001</v>
       </c>
       <c r="AH2">
-        <v>0.7905967154032026</v>
+        <v>0.7794280589369316</v>
       </c>
       <c r="AI2">
-        <v>0.8383999568681161</v>
+        <v>0.8080783736008916</v>
       </c>
       <c r="AJ2">
-        <v>0.7594481536850456</v>
+        <v>0.7529703744385655</v>
       </c>
       <c r="AK2">
-        <v>0.8126772911133101</v>
+        <v>0.7841053929334307</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Banco de Chile (SNSE:CHILE)</t>
+          <t>Scotiabank Chile S.A. (SNSE:SCOTIABKCL)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,13 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.112</v>
+        <v>0.0545</v>
       </c>
       <c r="E3">
-        <v>0.159</v>
-      </c>
-      <c r="F3">
-        <v>-0.0629</v>
+        <v>0.153</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,28 +731,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>1349</v>
+        <v>497.7</v>
       </c>
       <c r="L3">
-        <v>0.4665237238898879</v>
+        <v>0.3624644963950186</v>
       </c>
       <c r="M3">
-        <v>970.7</v>
+        <v>136.4</v>
       </c>
       <c r="N3">
-        <v>0.08137789961687752</v>
+        <v>0.04814344204433151</v>
       </c>
       <c r="O3">
-        <v>0.7195700518902891</v>
+        <v>0.2740606791239703</v>
       </c>
       <c r="P3">
-        <v>970.7</v>
+        <v>136.4</v>
       </c>
       <c r="Q3">
-        <v>0.08137789961687752</v>
+        <v>0.04814344204433151</v>
       </c>
       <c r="R3">
-        <v>0.7195700518902891</v>
+        <v>0.2740606791239703</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +761,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3233.2</v>
+        <v>1070.6</v>
       </c>
       <c r="V3">
-        <v>0.271052874257019</v>
+        <v>0.3778766059579274</v>
       </c>
       <c r="W3">
-        <v>0.276411769527088</v>
+        <v>0.1315796430931923</v>
       </c>
       <c r="X3">
-        <v>0.09195440810251884</v>
+        <v>0.1834943535326057</v>
       </c>
       <c r="Y3">
-        <v>0.1844573614245691</v>
+        <v>-0.05191471043941337</v>
       </c>
       <c r="Z3">
-        <v>0.1277806746975174</v>
+        <v>0.05007914335524059</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06041354841159265</v>
+        <v>0.06214896273617679</v>
       </c>
       <c r="AC3">
-        <v>-0.06041354841159265</v>
+        <v>-0.06214896273617679</v>
       </c>
       <c r="AD3">
-        <v>21457.2</v>
+        <v>20973.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>21457.2</v>
+        <v>20973.7</v>
       </c>
       <c r="AG3">
-        <v>18224</v>
+        <v>19903.1</v>
       </c>
       <c r="AH3">
-        <v>0.6427101586017883</v>
+        <v>0.880992485371888</v>
       </c>
       <c r="AI3">
-        <v>0.792211244517301</v>
+        <v>0.8346545370613565</v>
       </c>
       <c r="AJ3">
-        <v>0.6043983377719113</v>
+        <v>0.8753886956101037</v>
       </c>
       <c r="AK3">
-        <v>0.7640449438202247</v>
+        <v>0.8272965333776707</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -841,10 +838,10 @@
         <v>0.103</v>
       </c>
       <c r="E4">
-        <v>0.14</v>
+        <v>0.144</v>
       </c>
       <c r="F4">
-        <v>-0.0203</v>
+        <v>0.123</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,28 +856,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>775.4</v>
+        <v>904.6</v>
       </c>
       <c r="L4">
-        <v>0.334685773480663</v>
+        <v>0.3405617046909118</v>
       </c>
       <c r="M4">
-        <v>283.6</v>
+        <v>243.6</v>
       </c>
       <c r="N4">
-        <v>0.05466777184494093</v>
+        <v>0.04013377926421405</v>
       </c>
       <c r="O4">
-        <v>0.3657467113747743</v>
+        <v>0.2692902940526199</v>
       </c>
       <c r="P4">
-        <v>283.6</v>
+        <v>243.6</v>
       </c>
       <c r="Q4">
-        <v>0.05466777184494093</v>
+        <v>0.04013377926421405</v>
       </c>
       <c r="R4">
-        <v>0.3657467113747743</v>
+        <v>0.2692902940526199</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -889,55 +886,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>3836.3</v>
+        <v>3941</v>
       </c>
       <c r="V4">
-        <v>0.7394992000308422</v>
+        <v>0.6492907392457617</v>
       </c>
       <c r="W4">
-        <v>0.1531442565966187</v>
+        <v>0.1307452159333989</v>
       </c>
       <c r="X4">
-        <v>0.1638608914784369</v>
+        <v>0.1317203538836543</v>
       </c>
       <c r="Y4">
-        <v>-0.01071663488181812</v>
+        <v>-0.0009751379502554169</v>
       </c>
       <c r="Z4">
-        <v>0.07223701523437744</v>
+        <v>0.07671247119166853</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06079128207260086</v>
+        <v>0.06318570928075512</v>
       </c>
       <c r="AC4">
-        <v>-0.06079128207260086</v>
+        <v>-0.06318570928075512</v>
       </c>
       <c r="AD4">
-        <v>31569.4</v>
+        <v>24911.5</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>31569.4</v>
+        <v>24911.5</v>
       </c>
       <c r="AG4">
-        <v>27733.1</v>
+        <v>20970.5</v>
       </c>
       <c r="AH4">
-        <v>0.8588653620661043</v>
+        <v>0.8040844124824087</v>
       </c>
       <c r="AI4">
-        <v>0.8418798518348636</v>
+        <v>0.7784770767774052</v>
       </c>
       <c r="AJ4">
-        <v>0.842418774756385</v>
+        <v>0.7755305064311654</v>
       </c>
       <c r="AK4">
-        <v>0.8238598555064405</v>
+        <v>0.7473636191922108</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -963,13 +960,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.0109</v>
+        <v>0.0454</v>
       </c>
       <c r="E5">
-        <v>-0.0654</v>
+        <v>0.0507</v>
       </c>
       <c r="F5">
-        <v>0.04849999999999999</v>
+        <v>0.309</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -984,28 +981,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>453.4</v>
+        <v>844.7</v>
       </c>
       <c r="L5">
-        <v>0.2992936827513367</v>
+        <v>0.3918085254418108</v>
       </c>
       <c r="M5">
-        <v>543.3</v>
+        <v>387.2</v>
       </c>
       <c r="N5">
-        <v>0.05876245173431973</v>
+        <v>0.04318055090888814</v>
       </c>
       <c r="O5">
-        <v>1.198279664755183</v>
+        <v>0.4583875932283651</v>
       </c>
       <c r="P5">
-        <v>543.3</v>
+        <v>387.2</v>
       </c>
       <c r="Q5">
-        <v>0.05876245173431973</v>
+        <v>0.04318055090888814</v>
       </c>
       <c r="R5">
-        <v>1.198279664755183</v>
+        <v>0.4583875932283651</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1014,55 +1011,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>4972.6</v>
+        <v>2961.3</v>
       </c>
       <c r="V5">
-        <v>0.5378283959029603</v>
+        <v>0.3302442288390766</v>
       </c>
       <c r="W5">
-        <v>0.1127047652191205</v>
+        <v>0.1799262998700663</v>
       </c>
       <c r="X5">
-        <v>0.1326817962982215</v>
+        <v>0.1216209055958583</v>
       </c>
       <c r="Y5">
-        <v>-0.01997703107910097</v>
+        <v>0.05830539427420797</v>
       </c>
       <c r="Z5">
-        <v>0.03671310029275481</v>
+        <v>0.05556257135714526</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06084900905472118</v>
+        <v>0.06333034621545344</v>
       </c>
       <c r="AC5">
-        <v>-0.06084900905472118</v>
+        <v>-0.06333034621545344</v>
       </c>
       <c r="AD5">
-        <v>39079.2</v>
+        <v>31032.9</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>39079.2</v>
+        <v>31032.9</v>
       </c>
       <c r="AG5">
-        <v>34106.6</v>
+        <v>28071.6</v>
       </c>
       <c r="AH5">
-        <v>0.8086762724806467</v>
+        <v>0.7758244395610989</v>
       </c>
       <c r="AI5">
-        <v>0.8899090716564535</v>
+        <v>0.8655979961730923</v>
       </c>
       <c r="AJ5">
-        <v>0.786731038491614</v>
+        <v>0.7579012165686607</v>
       </c>
       <c r="AK5">
-        <v>0.8758509646620152</v>
+        <v>0.8534969489299211</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1088,10 +1085,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.04480000000000001</v>
+        <v>0.0364</v>
       </c>
       <c r="E6">
-        <v>0.24</v>
+        <v>0.199</v>
+      </c>
+      <c r="F6">
+        <v>0.109</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1106,28 +1106,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>414.5</v>
+        <v>401.7</v>
       </c>
       <c r="L6">
-        <v>0.3366907643570791</v>
+        <v>0.3057775747887646</v>
       </c>
       <c r="M6">
-        <v>145.7</v>
+        <v>118.6</v>
       </c>
       <c r="N6">
-        <v>0.06879456064970017</v>
+        <v>0.05360936581837906</v>
       </c>
       <c r="O6">
-        <v>0.3515078407720145</v>
+        <v>0.2952452078665671</v>
       </c>
       <c r="P6">
-        <v>145.7</v>
+        <v>118.6</v>
       </c>
       <c r="Q6">
-        <v>0.06879456064970017</v>
+        <v>0.05360936581837906</v>
       </c>
       <c r="R6">
-        <v>0.3515078407720145</v>
+        <v>0.2952452078665671</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1136,55 +1136,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>5503.3</v>
+        <v>4890.2</v>
       </c>
       <c r="V6">
-        <v>2.598470182728174</v>
+        <v>2.210459702571983</v>
       </c>
       <c r="W6">
-        <v>0.1202076445681805</v>
+        <v>0.09889704072086267</v>
       </c>
       <c r="X6">
-        <v>0.2189767928370019</v>
+        <v>0.1896726157915425</v>
       </c>
       <c r="Y6">
-        <v>-0.09876914826882144</v>
+        <v>-0.09077557507067985</v>
       </c>
       <c r="Z6">
-        <v>0.06944930217864677</v>
+        <v>0.07358015010641873</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.06161977638093022</v>
+        <v>0.06347654479208242</v>
       </c>
       <c r="AC6">
-        <v>-0.06161977638093022</v>
+        <v>-0.06347654479208242</v>
       </c>
       <c r="AD6">
-        <v>19847</v>
+        <v>17248.1</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>19847</v>
+        <v>17248.1</v>
       </c>
       <c r="AG6">
-        <v>14343.7</v>
+        <v>12357.9</v>
       </c>
       <c r="AH6">
-        <v>0.9035779812336955</v>
+        <v>0.8863178557480833</v>
       </c>
       <c r="AI6">
-        <v>0.8299843178254052</v>
+        <v>0.7987894112852432</v>
       </c>
       <c r="AJ6">
-        <v>0.8713430043252174</v>
+        <v>0.8481626882266544</v>
       </c>
       <c r="AK6">
-        <v>0.7791593333767899</v>
+        <v>0.7398788212613604</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Grupo Security S.A. (SNSE:SECURITY)</t>
+          <t>Banco Internacional (SNSE:BINT)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.04679999999999999</v>
+        <v>0.168</v>
       </c>
       <c r="E7">
-        <v>0.18</v>
+        <v>0.172</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1228,28 +1228,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>202.3</v>
+        <v>61</v>
       </c>
       <c r="L7">
-        <v>0.6656794998354723</v>
+        <v>0.3423120089786756</v>
       </c>
       <c r="M7">
-        <v>76.09999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="N7">
-        <v>0.06472189147814254</v>
+        <v>0.03702962369895917</v>
       </c>
       <c r="O7">
-        <v>0.3761739990113692</v>
+        <v>0.3032786885245902</v>
       </c>
       <c r="P7">
-        <v>76.09999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="Q7">
-        <v>0.06472189147814254</v>
+        <v>0.03702962369895917</v>
       </c>
       <c r="R7">
-        <v>0.3761739990113692</v>
+        <v>0.3032786885245902</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1258,60 +1258,185 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>792.5</v>
+        <v>108.5</v>
       </c>
       <c r="V7">
-        <v>0.6740091852355843</v>
+        <v>0.2171737389911929</v>
       </c>
       <c r="W7">
-        <v>0.2238574748257165</v>
+        <v>0.1679515418502203</v>
       </c>
       <c r="X7">
-        <v>0.06192751386767292</v>
+        <v>0.1473948475193236</v>
       </c>
       <c r="Y7">
-        <v>0.1619299609580436</v>
+        <v>0.02055669433089671</v>
       </c>
       <c r="Z7">
-        <v>0.04470103699345444</v>
+        <v>0.06656705267090025</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.06173185765722965</v>
+        <v>0.06369305355376179</v>
       </c>
       <c r="AC7">
-        <v>-0.06173185765722965</v>
+        <v>-0.06369305355376179</v>
       </c>
       <c r="AD7">
-        <v>10.4</v>
+        <v>2549.4</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>10.4</v>
+        <v>2549.4</v>
       </c>
       <c r="AG7">
-        <v>-782.1</v>
+        <v>2440.9</v>
       </c>
       <c r="AH7">
-        <v>0.008767492834260664</v>
+        <v>0.8361429977041653</v>
       </c>
       <c r="AI7">
-        <v>0.009172693596754277</v>
+        <v>0.8620992831056404</v>
       </c>
       <c r="AJ7">
-        <v>-1.986537973075946</v>
+        <v>0.8300969222921272</v>
       </c>
       <c r="AK7">
-        <v>-2.291532376208614</v>
+        <v>0.8568469828342752</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Banco de Chile (SNSE:CHILE)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.115</v>
+      </c>
+      <c r="E8">
+        <v>0.186</v>
+      </c>
+      <c r="F8">
+        <v>0.00086</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>1588.2</v>
+      </c>
+      <c r="L8">
+        <v>0.4914897567617751</v>
+      </c>
+      <c r="M8">
+        <v>909.2</v>
+      </c>
+      <c r="N8">
+        <v>0.07914000957479218</v>
+      </c>
+      <c r="O8">
+        <v>0.5724719808588339</v>
+      </c>
+      <c r="P8">
+        <v>909.2</v>
+      </c>
+      <c r="Q8">
+        <v>0.07914000957479218</v>
+      </c>
+      <c r="R8">
+        <v>0.5724719808588339</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>2600.8</v>
+      </c>
+      <c r="V8">
+        <v>0.2263829046437742</v>
+      </c>
+      <c r="W8">
+        <v>0.2821961620469083</v>
+      </c>
+      <c r="X8">
+        <v>0.08999422684674929</v>
+      </c>
+      <c r="Y8">
+        <v>0.192201935200159</v>
+      </c>
+      <c r="Z8">
+        <v>0.1354771088378333</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.0638440582537587</v>
+      </c>
+      <c r="AC8">
+        <v>-0.0638440582537587</v>
+      </c>
+      <c r="AD8">
+        <v>16610.2</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>16610.2</v>
+      </c>
+      <c r="AG8">
+        <v>14009.4</v>
+      </c>
+      <c r="AH8">
+        <v>0.5911376682907038</v>
+      </c>
+      <c r="AI8">
+        <v>0.7313789034292054</v>
+      </c>
+      <c r="AJ8">
+        <v>0.5494334827574036</v>
+      </c>
+      <c r="AK8">
+        <v>0.6966384883142716</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/chile/chile_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ8"/>
+  <dimension ref="A1:AQ9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.07875</v>
+        <v>0.062</v>
       </c>
       <c r="E2">
-        <v>0.1625</v>
+        <v>0.153</v>
       </c>
       <c r="F2">
         <v>0.116</v>
@@ -609,28 +609,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>4297.9</v>
+        <v>4475.1</v>
       </c>
       <c r="L2">
-        <v>0.3939955080900215</v>
+        <v>0.3866611368879442</v>
       </c>
       <c r="M2">
-        <v>1813.5</v>
+        <v>1935.4</v>
       </c>
       <c r="N2">
-        <v>0.0565476468882424</v>
+        <v>0.05841588342176908</v>
       </c>
       <c r="O2">
-        <v>0.4219502547755881</v>
+        <v>0.4324819557104869</v>
       </c>
       <c r="P2">
-        <v>1813.5</v>
+        <v>1935.4</v>
       </c>
       <c r="Q2">
-        <v>0.0565476468882424</v>
+        <v>0.05841588342176908</v>
       </c>
       <c r="R2">
-        <v>0.4219502547755881</v>
+        <v>0.4324819557104869</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>15572.4</v>
+        <v>16203.3</v>
       </c>
       <c r="V2">
-        <v>0.4855707617328182</v>
+        <v>0.4890617359966677</v>
       </c>
       <c r="W2">
-        <v>0.1497655924717063</v>
+        <v>0.1621967963386728</v>
       </c>
       <c r="X2">
-        <v>0.1395576007014889</v>
+        <v>0.1473532387848107</v>
       </c>
       <c r="Y2">
-        <v>0.01020799177021736</v>
+        <v>0.01484355755386207</v>
       </c>
       <c r="Z2">
-        <v>0.07511277072030727</v>
+        <v>0.07572433638074876</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06340344550376793</v>
+        <v>0.06332338492017042</v>
       </c>
       <c r="AC2">
-        <v>-0.06340344550376793</v>
+        <v>-0.06332338492017042</v>
       </c>
       <c r="AD2">
-        <v>113325.8</v>
+        <v>118925.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>113325.8</v>
+        <v>118925.1</v>
       </c>
       <c r="AG2">
-        <v>97753.40000000001</v>
+        <v>102721.8</v>
       </c>
       <c r="AH2">
-        <v>0.7794280589369316</v>
+        <v>0.7821112546980893</v>
       </c>
       <c r="AI2">
-        <v>0.8080783736008916</v>
+        <v>0.8085407118687626</v>
       </c>
       <c r="AJ2">
-        <v>0.7529703744385655</v>
+        <v>0.7561235215659255</v>
       </c>
       <c r="AK2">
-        <v>0.7841053929334307</v>
+        <v>0.7848380383060265</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Scotiabank Chile S.A. (SNSE:SCOTIABKCL)</t>
+          <t>Grupo Security S.A. (SNSE:SECURITY)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0545</v>
+        <v>0.062</v>
       </c>
       <c r="E3">
-        <v>0.153</v>
+        <v>0.137</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,28 +731,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>497.7</v>
+        <v>177.2</v>
       </c>
       <c r="L3">
-        <v>0.3624644963950186</v>
+        <v>0.2663860493084786</v>
       </c>
       <c r="M3">
-        <v>136.4</v>
+        <v>121.9</v>
       </c>
       <c r="N3">
-        <v>0.04814344204433151</v>
+        <v>0.11488078409198</v>
       </c>
       <c r="O3">
-        <v>0.2740606791239703</v>
+        <v>0.6879232505643341</v>
       </c>
       <c r="P3">
-        <v>136.4</v>
+        <v>121.9</v>
       </c>
       <c r="Q3">
-        <v>0.04814344204433151</v>
+        <v>0.11488078409198</v>
       </c>
       <c r="R3">
-        <v>0.2740606791239703</v>
+        <v>0.6879232505643341</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -761,55 +761,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1070.6</v>
+        <v>630.9</v>
       </c>
       <c r="V3">
-        <v>0.3778766059579274</v>
+        <v>0.5945716709075488</v>
       </c>
       <c r="W3">
-        <v>0.1315796430931923</v>
+        <v>0.1621967963386728</v>
       </c>
       <c r="X3">
-        <v>0.1834943535326057</v>
+        <v>0.1500831903598271</v>
       </c>
       <c r="Y3">
-        <v>-0.05191471043941337</v>
+        <v>0.01211360597884567</v>
       </c>
       <c r="Z3">
-        <v>0.05007914335524059</v>
+        <v>0.08739292658573757</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06214896273617679</v>
+        <v>0.0608436252430662</v>
       </c>
       <c r="AC3">
-        <v>-0.06214896273617679</v>
+        <v>-0.0608436252430662</v>
       </c>
       <c r="AD3">
-        <v>20973.7</v>
+        <v>5599.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>20973.7</v>
+        <v>5599.3</v>
       </c>
       <c r="AG3">
-        <v>19903.1</v>
+        <v>4968.400000000001</v>
       </c>
       <c r="AH3">
-        <v>0.880992485371888</v>
+        <v>0.8406852441294818</v>
       </c>
       <c r="AI3">
-        <v>0.8346545370613565</v>
+        <v>0.8180131482834185</v>
       </c>
       <c r="AJ3">
-        <v>0.8753886956101037</v>
+        <v>0.824015258313293</v>
       </c>
       <c r="AK3">
-        <v>0.8272965333776707</v>
+        <v>0.7995365378735457</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -826,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Banco de Crédito e Inversiones (SNSE:BCI)</t>
+          <t>Scotiabank Chile S.A. (SNSE:SCOTIABKCL)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -835,13 +835,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.103</v>
+        <v>0.0545</v>
       </c>
       <c r="E4">
-        <v>0.144</v>
-      </c>
-      <c r="F4">
-        <v>0.123</v>
+        <v>0.153</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,28 +853,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>904.6</v>
+        <v>497.7</v>
       </c>
       <c r="L4">
-        <v>0.3405617046909118</v>
+        <v>0.3624644963950186</v>
       </c>
       <c r="M4">
-        <v>243.6</v>
+        <v>136.4</v>
       </c>
       <c r="N4">
-        <v>0.04013377926421405</v>
+        <v>0.04814344204433151</v>
       </c>
       <c r="O4">
-        <v>0.2692902940526199</v>
+        <v>0.2740606791239703</v>
       </c>
       <c r="P4">
-        <v>243.6</v>
+        <v>136.4</v>
       </c>
       <c r="Q4">
-        <v>0.04013377926421405</v>
+        <v>0.04814344204433151</v>
       </c>
       <c r="R4">
-        <v>0.2692902940526199</v>
+        <v>0.2740606791239703</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -886,55 +883,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>3941</v>
+        <v>1070.6</v>
       </c>
       <c r="V4">
-        <v>0.6492907392457617</v>
+        <v>0.3778766059579274</v>
       </c>
       <c r="W4">
-        <v>0.1307452159333989</v>
+        <v>0.1315796430931923</v>
       </c>
       <c r="X4">
-        <v>0.1317203538836543</v>
+        <v>0.1834379600447472</v>
       </c>
       <c r="Y4">
-        <v>-0.0009751379502554169</v>
+        <v>-0.05185831695155491</v>
       </c>
       <c r="Z4">
-        <v>0.07671247119166853</v>
+        <v>0.05007914335524059</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06318570928075512</v>
+        <v>0.06214225148734554</v>
       </c>
       <c r="AC4">
-        <v>-0.06318570928075512</v>
+        <v>-0.06214225148734554</v>
       </c>
       <c r="AD4">
-        <v>24911.5</v>
+        <v>20973.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>24911.5</v>
+        <v>20973.7</v>
       </c>
       <c r="AG4">
-        <v>20970.5</v>
+        <v>19903.1</v>
       </c>
       <c r="AH4">
-        <v>0.8040844124824087</v>
+        <v>0.880992485371888</v>
       </c>
       <c r="AI4">
-        <v>0.7784770767774052</v>
+        <v>0.8346545370613565</v>
       </c>
       <c r="AJ4">
-        <v>0.7755305064311654</v>
+        <v>0.8753886956101037</v>
       </c>
       <c r="AK4">
-        <v>0.7473636191922108</v>
+        <v>0.8272965333776707</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -951,7 +948,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Banco Santander-Chile (SNSE:BSANTANDER)</t>
+          <t>Banco de Crédito e Inversiones (SNSE:BCI)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -960,13 +957,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0454</v>
+        <v>0.103</v>
       </c>
       <c r="E5">
-        <v>0.0507</v>
+        <v>0.144</v>
       </c>
       <c r="F5">
-        <v>0.309</v>
+        <v>0.123</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -981,28 +978,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>844.7</v>
+        <v>904.6</v>
       </c>
       <c r="L5">
-        <v>0.3918085254418108</v>
+        <v>0.3405617046909118</v>
       </c>
       <c r="M5">
-        <v>387.2</v>
+        <v>243.6</v>
       </c>
       <c r="N5">
-        <v>0.04318055090888814</v>
+        <v>0.04013377926421405</v>
       </c>
       <c r="O5">
-        <v>0.4583875932283651</v>
+        <v>0.2692902940526199</v>
       </c>
       <c r="P5">
-        <v>387.2</v>
+        <v>243.6</v>
       </c>
       <c r="Q5">
-        <v>0.04318055090888814</v>
+        <v>0.04013377926421405</v>
       </c>
       <c r="R5">
-        <v>0.4583875932283651</v>
+        <v>0.2692902940526199</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1011,55 +1008,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>2961.3</v>
+        <v>3941</v>
       </c>
       <c r="V5">
-        <v>0.3302442288390766</v>
+        <v>0.6492907392457617</v>
       </c>
       <c r="W5">
-        <v>0.1799262998700663</v>
+        <v>0.1307452159333989</v>
       </c>
       <c r="X5">
-        <v>0.1216209055958583</v>
+        <v>0.131685164725136</v>
       </c>
       <c r="Y5">
-        <v>0.05830539427420797</v>
+        <v>-0.0009399487917371163</v>
       </c>
       <c r="Z5">
-        <v>0.05556257135714526</v>
+        <v>0.07671247119166853</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06333034621545344</v>
+        <v>0.06317881517608975</v>
       </c>
       <c r="AC5">
-        <v>-0.06333034621545344</v>
+        <v>-0.06317881517608975</v>
       </c>
       <c r="AD5">
-        <v>31032.9</v>
+        <v>24911.5</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>31032.9</v>
+        <v>24911.5</v>
       </c>
       <c r="AG5">
-        <v>28071.6</v>
+        <v>20970.5</v>
       </c>
       <c r="AH5">
-        <v>0.7758244395610989</v>
+        <v>0.8040844124824087</v>
       </c>
       <c r="AI5">
-        <v>0.8655979961730923</v>
+        <v>0.7784770767774052</v>
       </c>
       <c r="AJ5">
-        <v>0.7579012165686607</v>
+        <v>0.7755305064311654</v>
       </c>
       <c r="AK5">
-        <v>0.8534969489299211</v>
+        <v>0.7473636191922108</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1076,7 +1073,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Banco Itaú Chile (SNSE:ITAUCL)</t>
+          <t>Banco Santander-Chile (SNSE:BSANTANDER)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1085,13 +1082,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0364</v>
+        <v>0.0454</v>
       </c>
       <c r="E6">
-        <v>0.199</v>
+        <v>0.0507</v>
       </c>
       <c r="F6">
-        <v>0.109</v>
+        <v>0.309</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1106,28 +1103,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>401.7</v>
+        <v>844.7</v>
       </c>
       <c r="L6">
-        <v>0.3057775747887646</v>
+        <v>0.3918085254418108</v>
       </c>
       <c r="M6">
-        <v>118.6</v>
+        <v>387.2</v>
       </c>
       <c r="N6">
-        <v>0.05360936581837906</v>
+        <v>0.04318055090888814</v>
       </c>
       <c r="O6">
-        <v>0.2952452078665671</v>
+        <v>0.4583875932283651</v>
       </c>
       <c r="P6">
-        <v>118.6</v>
+        <v>387.2</v>
       </c>
       <c r="Q6">
-        <v>0.05360936581837906</v>
+        <v>0.04318055090888814</v>
       </c>
       <c r="R6">
-        <v>0.2952452078665671</v>
+        <v>0.4583875932283651</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1136,55 +1133,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>4890.2</v>
+        <v>2961.3</v>
       </c>
       <c r="V6">
-        <v>2.210459702571983</v>
+        <v>0.3302442288390766</v>
       </c>
       <c r="W6">
-        <v>0.09889704072086267</v>
+        <v>0.1799262998700663</v>
       </c>
       <c r="X6">
-        <v>0.1896726157915425</v>
+        <v>0.1215898527225237</v>
       </c>
       <c r="Y6">
-        <v>-0.09077557507067985</v>
+        <v>0.05833644714754257</v>
       </c>
       <c r="Z6">
-        <v>0.07358015010641873</v>
+        <v>0.05556257135714526</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.06347654479208242</v>
+        <v>0.06332338492017042</v>
       </c>
       <c r="AC6">
-        <v>-0.06347654479208242</v>
+        <v>-0.06332338492017042</v>
       </c>
       <c r="AD6">
-        <v>17248.1</v>
+        <v>31032.9</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>17248.1</v>
+        <v>31032.9</v>
       </c>
       <c r="AG6">
-        <v>12357.9</v>
+        <v>28071.6</v>
       </c>
       <c r="AH6">
-        <v>0.8863178557480833</v>
+        <v>0.7758244395610989</v>
       </c>
       <c r="AI6">
-        <v>0.7987894112852432</v>
+        <v>0.8655979961730923</v>
       </c>
       <c r="AJ6">
-        <v>0.8481626882266544</v>
+        <v>0.7579012165686607</v>
       </c>
       <c r="AK6">
-        <v>0.7398788212613604</v>
+        <v>0.8534969489299211</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1201,7 +1198,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Banco Internacional (SNSE:BINT)</t>
+          <t>Banco Itaú Chile (SNSE:ITAUCL)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1210,10 +1207,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.168</v>
+        <v>0.0364</v>
       </c>
       <c r="E7">
-        <v>0.172</v>
+        <v>0.199</v>
+      </c>
+      <c r="F7">
+        <v>0.109</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1228,28 +1228,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>61</v>
+        <v>401.7</v>
       </c>
       <c r="L7">
-        <v>0.3423120089786756</v>
+        <v>0.3057775747887646</v>
       </c>
       <c r="M7">
-        <v>18.5</v>
+        <v>118.6</v>
       </c>
       <c r="N7">
-        <v>0.03702962369895917</v>
+        <v>0.05360936581837906</v>
       </c>
       <c r="O7">
-        <v>0.3032786885245902</v>
+        <v>0.2952452078665671</v>
       </c>
       <c r="P7">
-        <v>18.5</v>
+        <v>118.6</v>
       </c>
       <c r="Q7">
-        <v>0.03702962369895917</v>
+        <v>0.05360936581837906</v>
       </c>
       <c r="R7">
-        <v>0.3032786885245902</v>
+        <v>0.2952452078665671</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1258,55 +1258,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>108.5</v>
+        <v>4890.2</v>
       </c>
       <c r="V7">
-        <v>0.2171737389911929</v>
+        <v>2.210459702571983</v>
       </c>
       <c r="W7">
-        <v>0.1679515418502203</v>
+        <v>0.09889704072086267</v>
       </c>
       <c r="X7">
-        <v>0.1473948475193236</v>
+        <v>0.1896136919620343</v>
       </c>
       <c r="Y7">
-        <v>0.02055669433089671</v>
+        <v>-0.09071665124117159</v>
       </c>
       <c r="Z7">
-        <v>0.06656705267090025</v>
+        <v>0.07358015010641873</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.06369305355376179</v>
+        <v>0.06346984620479638</v>
       </c>
       <c r="AC7">
-        <v>-0.06369305355376179</v>
+        <v>-0.06346984620479638</v>
       </c>
       <c r="AD7">
-        <v>2549.4</v>
+        <v>17248.1</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>2549.4</v>
+        <v>17248.1</v>
       </c>
       <c r="AG7">
-        <v>2440.9</v>
+        <v>12357.9</v>
       </c>
       <c r="AH7">
-        <v>0.8361429977041653</v>
+        <v>0.8863178557480833</v>
       </c>
       <c r="AI7">
-        <v>0.8620992831056404</v>
+        <v>0.7987894112852432</v>
       </c>
       <c r="AJ7">
-        <v>0.8300969222921272</v>
+        <v>0.8481626882266544</v>
       </c>
       <c r="AK7">
-        <v>0.8568469828342752</v>
+        <v>0.7398788212613604</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1323,120 +1323,242 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>Banco Internacional (SNSE:BINT)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.168</v>
+      </c>
+      <c r="E8">
+        <v>0.172</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>61</v>
+      </c>
+      <c r="L8">
+        <v>0.3423120089786756</v>
+      </c>
+      <c r="M8">
+        <v>18.5</v>
+      </c>
+      <c r="N8">
+        <v>0.03702962369895917</v>
+      </c>
+      <c r="O8">
+        <v>0.3032786885245902</v>
+      </c>
+      <c r="P8">
+        <v>18.5</v>
+      </c>
+      <c r="Q8">
+        <v>0.03702962369895917</v>
+      </c>
+      <c r="R8">
+        <v>0.3032786885245902</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>108.5</v>
+      </c>
+      <c r="V8">
+        <v>0.2171737389911929</v>
+      </c>
+      <c r="W8">
+        <v>0.1679515418502203</v>
+      </c>
+      <c r="X8">
+        <v>0.1473532387848107</v>
+      </c>
+      <c r="Y8">
+        <v>0.02059830306540958</v>
+      </c>
+      <c r="Z8">
+        <v>0.06656705267090025</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.0636862356712552</v>
+      </c>
+      <c r="AC8">
+        <v>-0.0636862356712552</v>
+      </c>
+      <c r="AD8">
+        <v>2549.4</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>2549.4</v>
+      </c>
+      <c r="AG8">
+        <v>2440.9</v>
+      </c>
+      <c r="AH8">
+        <v>0.8361429977041653</v>
+      </c>
+      <c r="AI8">
+        <v>0.8620992831056404</v>
+      </c>
+      <c r="AJ8">
+        <v>0.8300969222921272</v>
+      </c>
+      <c r="AK8">
+        <v>0.8568469828342752</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>Banco de Chile (SNSE:CHILE)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D8">
+      <c r="D9">
         <v>0.115</v>
       </c>
-      <c r="E8">
+      <c r="E9">
         <v>0.186</v>
       </c>
-      <c r="F8">
+      <c r="F9">
         <v>0.00086</v>
       </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
         <v>1588.2</v>
       </c>
-      <c r="L8">
+      <c r="L9">
         <v>0.4914897567617751</v>
       </c>
-      <c r="M8">
+      <c r="M9">
         <v>909.2</v>
       </c>
-      <c r="N8">
+      <c r="N9">
         <v>0.07914000957479218</v>
       </c>
-      <c r="O8">
+      <c r="O9">
         <v>0.5724719808588339</v>
       </c>
-      <c r="P8">
+      <c r="P9">
         <v>909.2</v>
       </c>
-      <c r="Q8">
+      <c r="Q9">
         <v>0.07914000957479218</v>
       </c>
-      <c r="R8">
+      <c r="R9">
         <v>0.5724719808588339</v>
       </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
         <v>2600.8</v>
       </c>
-      <c r="V8">
+      <c r="V9">
         <v>0.2263829046437742</v>
       </c>
-      <c r="W8">
+      <c r="W9">
         <v>0.2821961620469083</v>
       </c>
-      <c r="X8">
-        <v>0.08999422684674929</v>
-      </c>
-      <c r="Y8">
-        <v>0.192201935200159</v>
-      </c>
-      <c r="Z8">
+      <c r="X9">
+        <v>0.08997612685549217</v>
+      </c>
+      <c r="Y9">
+        <v>0.1922200351914162</v>
+      </c>
+      <c r="Z9">
         <v>0.1354771088378333</v>
       </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0.0638440582537587</v>
-      </c>
-      <c r="AC8">
-        <v>-0.0638440582537587</v>
-      </c>
-      <c r="AD8">
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0.0638366578491294</v>
+      </c>
+      <c r="AC9">
+        <v>-0.0638366578491294</v>
+      </c>
+      <c r="AD9">
         <v>16610.2</v>
       </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
         <v>16610.2</v>
       </c>
-      <c r="AG8">
+      <c r="AG9">
         <v>14009.4</v>
       </c>
-      <c r="AH8">
+      <c r="AH9">
         <v>0.5911376682907038</v>
       </c>
-      <c r="AI8">
+      <c r="AI9">
         <v>0.7313789034292054</v>
       </c>
-      <c r="AJ8">
+      <c r="AJ9">
         <v>0.5494334827574036</v>
       </c>
-      <c r="AK8">
+      <c r="AK9">
         <v>0.6966384883142716</v>
       </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
         <v>0</v>
       </c>
     </row>
